--- a/budgetford-2026.xlsx
+++ b/budgetford-2026.xlsx
@@ -1,21 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucas\OneDrive\Bureau\CODE HTML\Developpements\APP KENT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucas\OneDrive\Bureau\CODE HTML\Developpements\APP KENT VERCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37DB1A50-5CFB-4667-A9ED-CA3C37828814}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1ADE2BC-1943-499A-B169-F8F97C2329CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Budget2026" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -83,6 +96,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="_-* #,##0\ &quot;€&quot;_-;\-* #,##0\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
+  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -112,8 +128,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -453,8 +470,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P74"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:P2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="30.83203125" customWidth="1"/>
     <col min="2" max="14" width="14.83203125" customWidth="1"/>
@@ -462,7 +479,7 @@
     <col min="16" max="16" width="40.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -512,132 +529,61 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>16</v>
       </c>
       <c r="B2" t="s">
         <v>17</v>
       </c>
-      <c r="C2">
-        <v>3500</v>
-      </c>
-      <c r="D2">
-        <v>3500</v>
-      </c>
-      <c r="E2">
-        <v>3500</v>
-      </c>
-      <c r="F2">
-        <v>3500</v>
-      </c>
-      <c r="G2">
-        <v>3500</v>
-      </c>
-      <c r="H2">
-        <v>3500</v>
-      </c>
-      <c r="I2">
-        <v>3500</v>
-      </c>
-      <c r="J2">
-        <v>3500</v>
-      </c>
-      <c r="K2">
-        <v>3500</v>
-      </c>
-      <c r="L2">
-        <v>3500</v>
-      </c>
-      <c r="M2">
-        <v>3500</v>
-      </c>
-      <c r="N2">
-        <v>3500</v>
-      </c>
-      <c r="O2">
-        <v>42000</v>
+      <c r="C2" s="1">
+        <v>769.02</v>
+      </c>
+      <c r="D2" s="1">
+        <v>769.02</v>
+      </c>
+      <c r="E2" s="1">
+        <v>854.30000000000007</v>
+      </c>
+      <c r="F2" s="1">
+        <v>749.66</v>
+      </c>
+      <c r="G2" s="1">
+        <v>555.4</v>
+      </c>
+      <c r="H2" s="1">
+        <v>875.82</v>
+      </c>
+      <c r="I2" s="1">
+        <v>790.38</v>
+      </c>
+      <c r="J2" s="1">
+        <v>427.24</v>
+      </c>
+      <c r="K2" s="1">
+        <v>918.54</v>
+      </c>
+      <c r="L2" s="1">
+        <v>875.82</v>
+      </c>
+      <c r="M2" s="1">
+        <v>790.38</v>
+      </c>
+      <c r="N2" s="1">
+        <v>726.30000000000007</v>
+      </c>
+      <c r="O2" s="1">
+        <f>+SUM(C2:N2)</f>
+        <v>9101.8799999999992</v>
       </c>
       <c r="P2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="4" spans="1:16" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="5" spans="1:16" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="6" spans="1:16" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="7" spans="1:16" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="8" spans="1:16" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="9" spans="1:16" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="10" spans="1:16" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="11" spans="1:16" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="12" spans="1:16" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="13" spans="1:16" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="14" spans="1:16" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="15" spans="1:16" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="16" spans="1:16" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="17" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="18" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="19" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="20" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="21" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="22" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="23" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="24" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="25" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="26" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="27" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="28" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="29" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="30" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="31" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="32" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="33" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="34" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="35" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="36" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="37" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="38" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="39" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="40" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="41" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="42" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="43" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="44" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="45" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="46" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="47" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="48" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="49" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="50" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="51" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="52" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="53" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="54" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="55" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="56" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="57" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="58" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="59" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="60" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="61" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="62" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="63" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="64" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="65" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="66" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="67" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="68" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="69" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="70" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="71" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="72" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="73" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="74" ht="15.5" x14ac:dyDescent="0.35"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:P2" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:P1 A2:B2 P2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>